--- a/outputs/daily/hr_rankings_2026-09-27_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-27_full.xlsx
@@ -3061,7 +3061,7 @@
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -16419,27 +16419,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>624424</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Michael Conforto</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-27T19:05:00Z</t>
+          <t>2026-09-27T18:30:00Z</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -16449,17 +16449,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Tanner Houck</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>656557</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16482,26 +16482,26 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>45.8</v>
+        <v>48.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>52</v>
+        <v>33.8</v>
       </c>
       <c r="R58" t="n">
-        <v>41.1</v>
+        <v>52.8</v>
       </c>
       <c r="S58" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T58" t="n">
         <v>80</v>
       </c>
       <c r="U58" t="n">
-        <v>39.5</v>
+        <v>12</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -16533,14 +16533,10 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -16557,27 +16553,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -16587,112 +16583,112 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>90.25</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>100.6403</t>
+          <t>101.6224</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.4836</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.1931</t>
+          <t>0.2135</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3764</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>32.94</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.2005</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>0.4093</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.1495</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16703,27 +16699,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>624424</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Michael Conforto</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-27T18:30:00Z</t>
+          <t>2026-09-27T19:05:00Z</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -16733,17 +16729,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Tanner Houck</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>656557</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16766,26 +16762,26 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>48.8</v>
+        <v>45.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>33.8</v>
+        <v>52</v>
       </c>
       <c r="R59" t="n">
-        <v>52.8</v>
+        <v>41.1</v>
       </c>
       <c r="S59" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T59" t="n">
         <v>80</v>
       </c>
       <c r="U59" t="n">
-        <v>12</v>
+        <v>37.8</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16799,7 +16795,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -16809,7 +16805,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -16817,10 +16813,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>order MLB 6 vs RotoWire 5</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2025</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -16837,27 +16837,27 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -16867,112 +16867,112 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.25</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>101.6224</t>
+          <t>100.6403</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.4836</t>
+          <t>0.4275</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.2135</t>
+          <t>0.1931</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.3764</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>72.92</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>32.94</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2005</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>0.4093</t>
+          <t>0.491</t>
         </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>0.1495</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr"/>
@@ -25412,7 +25412,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -27080,7 +27080,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -29892,7 +29892,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -30147,27 +30147,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>695670</t>
+          <t>681393</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Harry Ford</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-27T17:05:00Z</t>
+          <t>2026-09-27T19:10:00Z</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -30177,17 +30177,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Sean Manaea</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>640455</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -30210,26 +30210,26 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>40.3</v>
+        <v>30.5</v>
       </c>
       <c r="Q107" t="n">
-        <v>54.3</v>
+        <v>41.2</v>
       </c>
       <c r="R107" t="n">
-        <v>50.7</v>
+        <v>46.1</v>
       </c>
       <c r="S107" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T107" t="n">
         <v>78</v>
       </c>
       <c r="U107" t="n">
-        <v>16.6</v>
+        <v>23.7</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -30264,7 +30264,7 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr"/>
@@ -30281,12 +30281,12 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -30296,12 +30296,12 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 20.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
@@ -30311,97 +30311,97 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>87.25</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>99.0803</t>
+          <t>98.1726</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3799</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>0.2856</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>35.21</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>0.1078</t>
+          <t>0.1352</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>0.4367</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
-          <t>0.1869</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr">
@@ -30411,12 +30411,12 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr"/>
@@ -30427,27 +30427,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>681393</t>
+          <t>695670</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Harry Ford</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-27T19:10:00Z</t>
+          <t>2026-09-27T17:05:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -30457,17 +30457,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Sean Manaea</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>640455</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -30476,7 +30476,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -30490,26 +30490,26 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>30.5</v>
+        <v>40.3</v>
       </c>
       <c r="Q108" t="n">
-        <v>41.2</v>
+        <v>54.3</v>
       </c>
       <c r="R108" t="n">
-        <v>46.1</v>
+        <v>50.7</v>
       </c>
       <c r="S108" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T108" t="n">
         <v>78</v>
       </c>
       <c r="U108" t="n">
-        <v>23.7</v>
+        <v>14.1</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -30544,7 +30544,7 @@
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr"/>
@@ -30561,12 +30561,12 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -30576,12 +30576,12 @@
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 21.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 20.0 HR allowed</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
@@ -30591,97 +30591,97 @@
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>14.57</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>87.25</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>98.1726</t>
+          <t>99.0803</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>0.3799</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.2856</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>36.28</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>0.1352</t>
+          <t>0.1078</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.4367</t>
         </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.1869</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr">
@@ -30691,12 +30691,12 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr"/>
@@ -30707,27 +30707,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-27T19:05:00Z</t>
+          <t>2026-09-27T19:10:00Z</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -30737,17 +30737,17 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Seth Johnson</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>686751</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -30770,26 +30770,26 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>18.2</v>
+        <v>36.7</v>
       </c>
       <c r="Q109" t="n">
-        <v>48.9</v>
+        <v>25.3</v>
       </c>
       <c r="R109" t="n">
-        <v>60.9</v>
+        <v>45.1</v>
       </c>
       <c r="S109" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T109" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U109" t="n">
-        <v>80.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -30841,27 +30841,27 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.1% barrel, 4.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -30871,112 +30871,112 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>97.0057</t>
+          <t>100.4077</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>0.3758</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>51.65</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>0.1914</t>
+          <t>0.1729</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>0.3669</t>
+          <t>0.3845</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>0.1444</t>
+          <t>0.1279</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr"/>
@@ -30987,47 +30987,47 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>687637</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-27T19:10:00Z</t>
+          <t>2026-09-27T17:05:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>Delayed Start</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Elmer Rodríguez</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>695684</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -31036,7 +31036,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -31050,26 +31050,26 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>36.7</v>
+        <v>32.9</v>
       </c>
       <c r="Q110" t="n">
-        <v>25.3</v>
+        <v>31.6</v>
       </c>
       <c r="R110" t="n">
-        <v>45.1</v>
+        <v>54.7</v>
       </c>
       <c r="S110" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T110" t="n">
         <v>80</v>
       </c>
       <c r="U110" t="n">
-        <v>70.59999999999999</v>
+        <v>39.4</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -31104,7 +31104,7 @@
       <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr"/>
@@ -31121,12 +31121,12 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -31141,7 +31141,7 @@
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
@@ -31151,77 +31151,77 @@
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>35.21</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>100.4077</t>
+          <t>99.1677</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3807</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1635</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>0.1729</t>
+          <t>0.1534</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
@@ -31231,32 +31231,32 @@
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>0.3845</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>0.1279</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI110" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ110" t="inlineStr"/>
@@ -31267,47 +31267,47 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>687637</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-27T17:05:00Z</t>
+          <t>2026-09-27T19:05:00Z</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Delayed Start</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Elmer Rodríguez</t>
+          <t>Seth Johnson</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>695684</t>
+          <t>686751</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -31330,26 +31330,26 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>32.9</v>
+        <v>18.2</v>
       </c>
       <c r="Q111" t="n">
-        <v>31.6</v>
+        <v>48.9</v>
       </c>
       <c r="R111" t="n">
-        <v>54.7</v>
+        <v>60.9</v>
       </c>
       <c r="S111" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T111" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U111" t="n">
-        <v>39.4</v>
+        <v>79</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -31384,7 +31384,7 @@
       <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr"/>
@@ -31401,27 +31401,27 @@
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.1% barrel, 4.4 HR allowed</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
@@ -31431,112 +31431,112 @@
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>30.73</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>99.1677</t>
+          <t>97.0057</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>0.3807</t>
+          <t>0.3758</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>0.1635</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>51.65</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>0.1534</t>
+          <t>0.1914</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.3669</t>
         </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.1444</t>
         </is>
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BG111" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BI111" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ111" t="inlineStr"/>
@@ -31547,22 +31547,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -31577,17 +31577,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -31610,26 +31610,26 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>24</v>
+        <v>38.2</v>
       </c>
       <c r="Q112" t="n">
-        <v>60.1</v>
+        <v>46.4</v>
       </c>
       <c r="R112" t="n">
-        <v>46.1</v>
+        <v>29.6</v>
       </c>
       <c r="S112" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T112" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U112" t="n">
-        <v>45</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -31664,7 +31664,7 @@
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr"/>
@@ -31681,7 +31681,7 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
@@ -31696,12 +31696,12 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Contact streak: 10/22 over last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.6% barrel, 25.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 19.3 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -31711,112 +31711,112 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>100.1023</t>
+          <t>100.7372</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1752</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>27.68</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>0.3933</t>
         </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
-          <t>0.2001</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI112" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ112" t="inlineStr"/>
@@ -31827,24 +31827,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>2026-09-27T19:10:00Z</t>
@@ -31857,17 +31857,17 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -31876,7 +31876,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -31890,26 +31890,26 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>29.1</v>
+        <v>24</v>
       </c>
       <c r="Q113" t="n">
-        <v>39.2</v>
+        <v>60.1</v>
       </c>
       <c r="R113" t="n">
         <v>46.1</v>
       </c>
       <c r="S113" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T113" t="n">
         <v>75</v>
       </c>
       <c r="U113" t="n">
-        <v>54.3</v>
+        <v>45</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -31944,7 +31944,7 @@
       <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr"/>
@@ -31961,27 +31961,27 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 10/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 21.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.6% barrel, 25.5 HR allowed</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -31991,97 +31991,97 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>99.1475</t>
+          <t>100.1023</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.391</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>44.99</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.487</t>
         </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.2001</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr">
@@ -32107,22 +32107,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -32142,12 +32142,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -32156,7 +32156,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -32174,22 +32174,22 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>38.2</v>
+        <v>29.1</v>
       </c>
       <c r="Q114" t="n">
-        <v>46.4</v>
+        <v>39.2</v>
       </c>
       <c r="R114" t="n">
-        <v>29.6</v>
+        <v>46.1</v>
       </c>
       <c r="S114" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T114" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U114" t="n">
-        <v>3.4</v>
+        <v>54.3</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
       <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr"/>
@@ -32241,27 +32241,27 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 19.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -32271,112 +32271,112 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>100.7372</t>
+          <t>99.1475</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.1752</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>27.68</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.191</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.3933</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -36875,27 +36875,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-27T17:05:00Z</t>
+          <t>2026-09-27T19:10:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -36905,17 +36905,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Sean Manaea</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>640455</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -36942,22 +36942,22 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>36.3</v>
+        <v>18.8</v>
       </c>
       <c r="Q131" t="n">
-        <v>54.3</v>
+        <v>61.5</v>
       </c>
       <c r="R131" t="n">
-        <v>50.7</v>
+        <v>46.1</v>
       </c>
       <c r="S131" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T131" t="n">
         <v>50</v>
       </c>
       <c r="U131" t="n">
-        <v>9.300000000000001</v>
+        <v>42</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -36992,7 +36992,7 @@
       <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr"/>
@@ -37009,12 +37009,12 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -37024,12 +37024,12 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Contact streak: 10/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 20.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 25.5 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
@@ -37039,97 +37039,97 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>99.0897</t>
+          <t>97.5114</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.4462</t>
+          <t>0.397</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.1754</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.3326</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>70.78</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1885</t>
+          <t>0.117</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>44.99</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.4367</t>
+          <t>0.487</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.1869</t>
+          <t>0.2001</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
@@ -37139,12 +37139,12 @@
       </c>
       <c r="BH131" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr"/>
@@ -37155,27 +37155,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-27T19:10:00Z</t>
+          <t>2026-09-27T17:05:00Z</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -37185,17 +37185,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Sean Manaea</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>640455</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -37204,7 +37204,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -37222,22 +37222,22 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>18.8</v>
+        <v>36.3</v>
       </c>
       <c r="Q132" t="n">
-        <v>61.5</v>
+        <v>54.3</v>
       </c>
       <c r="R132" t="n">
-        <v>46.1</v>
+        <v>50.7</v>
       </c>
       <c r="S132" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T132" t="n">
         <v>50</v>
       </c>
       <c r="U132" t="n">
-        <v>42</v>
+        <v>8.1</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -37272,7 +37272,7 @@
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr"/>
@@ -37289,12 +37289,12 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -37304,12 +37304,12 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 25.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 20.0 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -37319,97 +37319,97 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>97.5114</t>
+          <t>99.0897</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>0.4462</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1754</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3326</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.78</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.1885</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="BD132" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>0.4367</t>
         </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
-          <t>0.2001</t>
+          <t>0.1869</t>
         </is>
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr">
@@ -37419,12 +37419,12 @@
       </c>
       <c r="BH132" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -38604,7 +38604,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>78</v>
       </c>
       <c r="U137" t="n">
-        <v>40.3</v>
+        <v>37.3</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -38704,7 +38704,7 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Contact streak: 7/19 over last 7 games</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
@@ -39980,7 +39980,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -41944,7 +41944,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -42504,7 +42504,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -45559,27 +45559,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>621020</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-27T18:30:00Z</t>
+          <t>2026-09-27T19:05:00Z</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -45589,17 +45589,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Tanner Houck</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>656557</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -45622,26 +45622,26 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>26.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q162" t="n">
-        <v>33.8</v>
+        <v>52</v>
       </c>
       <c r="R162" t="n">
-        <v>52.8</v>
+        <v>41.1</v>
       </c>
       <c r="S162" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>20.9</v>
+        <v>26.4</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
@@ -45665,7 +45665,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -45673,10 +45673,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>order MLB 9 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2025</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr"/>
@@ -45693,27 +45697,27 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -45723,112 +45727,112 @@
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>89.73</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>99.2398</t>
+          <t>99.9083</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>0.3764</t>
+          <t>0.4098</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3149</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>0.1418</t>
+          <t>0.1821</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>0.4093</t>
+          <t>0.491</t>
         </is>
       </c>
       <c r="BE162" t="inlineStr">
         <is>
-          <t>0.1495</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BG162" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH162" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI162" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ162" t="inlineStr"/>
@@ -45839,27 +45843,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-27T19:05:00Z</t>
+          <t>2026-09-27T18:30:00Z</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -45869,17 +45873,17 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Tanner Houck</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>656557</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -45888,7 +45892,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -45902,26 +45906,26 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P163" t="n">
-        <v>38.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q163" t="n">
-        <v>52</v>
+        <v>33.8</v>
       </c>
       <c r="R163" t="n">
-        <v>41.1</v>
+        <v>52.8</v>
       </c>
       <c r="S163" t="n">
-        <v>44.8</v>
+        <v>93.2</v>
       </c>
       <c r="T163" t="n">
         <v>50</v>
       </c>
       <c r="U163" t="n">
-        <v>26.4</v>
+        <v>19.5</v>
       </c>
       <c r="V163" t="inlineStr">
         <is>
@@ -45935,7 +45939,7 @@
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y163" t="inlineStr">
@@ -45945,7 +45949,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -45953,14 +45957,10 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB163" t="inlineStr"/>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr"/>
@@ -45977,27 +45977,27 @@
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 1 HR</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM163" t="inlineStr">
@@ -46007,112 +46007,112 @@
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>89.73</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>99.9083</t>
+          <t>99.2398</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
         <is>
-          <t>0.4098</t>
+          <t>0.3764</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>0.1821</t>
+          <t>0.1418</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="BD163" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>0.4093</t>
         </is>
       </c>
       <c r="BE163" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.1495</t>
         </is>
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG163" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH163" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI163" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ163" t="inlineStr"/>
@@ -48948,7 +48948,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -56236,7 +56236,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -62510,7 +62510,7 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -62520,7 +62520,7 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/18, 0 HR</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
@@ -65813,7 +65813,7 @@
         <v>50</v>
       </c>
       <c r="U234" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -65874,7 +65874,7 @@
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
@@ -65884,7 +65884,7 @@
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
@@ -68840,7 +68840,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -72484,7 +72484,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -73044,7 +73044,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -73604,7 +73604,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -74444,7 +74444,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -74724,7 +74724,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -75004,7 +75004,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -79031,7 +79031,7 @@
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -79088,7 +79088,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -79098,7 +79098,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
